--- a/data-manipulation-scripts/sheets-cleanup/sheets/ESTRIBO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ESTRIBO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>ESTRIBO BIZ125</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -122,7 +119,7 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -393,7 +390,9 @@
       <c r="C2" s="4">
         <v>3.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="5">
+        <v>80.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -425,7 +424,9 @@
       <c r="C3" s="4">
         <v>2.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="5">
+        <v>80.0</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -457,7 +458,9 @@
       <c r="C4" s="4">
         <v>1.0</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="5">
+        <v>80.0</v>
+      </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -491,7 +494,9 @@
       <c r="C5" s="8">
         <v>1.0</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="5">
+        <v>80.0</v>
+      </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -525,7 +530,9 @@
       <c r="C6" s="8">
         <v>1.0</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="5">
+        <v>80.0</v>
+      </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -559,7 +566,9 @@
       <c r="C7" s="8">
         <v>1.0</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="5">
+        <v>70.0</v>
+      </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -593,7 +602,9 @@
       <c r="C8" s="8">
         <v>5.0</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="5">
+        <v>65.0</v>
+      </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -627,8 +638,8 @@
       <c r="C9" s="8">
         <v>1.0</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>16</v>
+      <c r="D9" s="5">
+        <v>80.0</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
